--- a/data/trans_orig/IP11A_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP11A_R-Clase-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -836,47 +836,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3960</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>5857</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>3960</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3960</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3960</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3960</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>5857</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>5857</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>5857</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>3960</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>3960</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>3960</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1184,42 +1184,42 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>5628</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>6039</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>5628</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1297,52 +1297,52 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>5628</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>5628</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>5628</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>6039</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>6039</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>6039</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>5628</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>5628</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>5628</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1522,47 +1522,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>8616</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>3778</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>8616</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8616</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>8616</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>8616</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>3778</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>3778</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>3778</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>8616</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>8616</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>8616</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,107 +1752,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>695</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>695</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2848</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4050</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>19,6%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3467</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13838</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>11021</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>14533</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,22%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>75,83%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>12716</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>13838</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>11685</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>14533</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,22%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23782</t>
+          <t>23199</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>14533</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>14533</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>14533</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>12716</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>12716</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>12716</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>14533</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>14533</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>14533</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,107 +2095,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3828</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>10,11%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1131</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3684</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>10,11%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3714</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>8,05%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>32,92%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1131</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4277</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>8,05%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>26,45%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>10059</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>7362</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>11190</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>89,89%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>65,79%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>2856</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>10059</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>7506</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>11190</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>89,89%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9769</t>
+          <t>10332</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>11190</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>11190</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>11190</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>2856</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>2856</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>2856</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>11190</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>11190</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>11190</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2551,47 +2551,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>2840</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1237</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2664,57 +2664,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>2840</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>2840</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>2840</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>1237</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>1237</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>1237</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2781,92 +2781,92 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4644</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>4,04%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>1826</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>485</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>4991</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>11,05%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>482</t>
-        </is>
-      </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4952</t>
+          <t>4864</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -2894,72 +2894,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>43337</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>40519</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>45163</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>95,96%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>89,72%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>34085</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>43337</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>40172</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>44678</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>95,96%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>74297</t>
+          <t>74385</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>78767</t>
+          <t>78764</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3007,57 +3007,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>45163</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>45163</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>45163</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>34085</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>34085</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>34085</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>45163</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>45163</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>45163</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3179,7 +3179,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3190,7 +3190,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3471,47 +3471,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8925</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>4673</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>8925</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -3584,57 +3584,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8925</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8925</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8925</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>4673</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>4673</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>4673</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>8925</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>8925</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>8925</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3814,47 +3814,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9428</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>7704</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>9428</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -3927,57 +3927,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>9428</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>9428</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>9428</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>7704</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>7704</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>7704</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>9428</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>9428</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>9428</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4162,42 +4162,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>6074</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>6232</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>6074</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4275,52 +4275,52 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>6074</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6074</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>6074</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>6232</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>6232</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>6232</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>6074</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>6074</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>6074</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4387,107 +4387,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>628</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>628</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3568</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3626</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>14,71%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>628</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2599</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -4500,72 +4500,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>23628</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>21588</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>24256</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,41%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>89,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>15854</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>23628</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>20688</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>24256</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,41%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37511</t>
+          <t>36484</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4613,57 +4613,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>24256</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>24256</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>24256</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>15854</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>15854</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>15854</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>24256</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>24256</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>24256</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4730,107 +4730,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>641</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>641</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2939</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3331</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>21,71%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3268</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,43%</t>
         </is>
       </c>
     </row>
@@ -4843,72 +4843,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>12897</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>10681</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>13538</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>95,26%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>78,89%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>13260</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>12897</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>10599</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>13538</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>95,26%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23530</t>
+          <t>23467</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4956,57 +4956,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>13538</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>13538</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>13538</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>13260</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>13260</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>13260</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>13538</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>13538</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>13538</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5186,47 +5186,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>9230</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>2043</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>9230</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5299,57 +5299,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>9230</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>9230</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>9230</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>2043</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>2043</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>2043</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>9230</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>9230</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>9230</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5416,107 +5416,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>1269</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>4451</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>4322</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>6,23%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1269</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>4449</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -5529,72 +5529,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>70181</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>67519</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>71450</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>98,22%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>94,5%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>49767</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>70181</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>66999</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>71450</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>98,22%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>116768</t>
+          <t>116895</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -5642,57 +5642,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>71450</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>71450</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>71450</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>49767</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>49767</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>49767</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>71450</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>71450</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>71450</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5814,7 +5814,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5825,7 +5825,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6106,47 +6106,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2746</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>4162</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2746</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -6219,57 +6219,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2746</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2746</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2746</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>4162</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>4162</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>4162</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2746</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2746</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2746</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6449,47 +6449,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5904</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>2065</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>5904</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -6562,57 +6562,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>5904</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>5904</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>5904</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>2065</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>2065</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>2065</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>5904</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>5904</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>5904</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6679,107 +6679,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>713</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3284</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>12,54%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>713</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2922</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>12,54%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>2916</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>11,17%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>51,37%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>2951</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>11,17%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>45,67%</t>
         </is>
       </c>
     </row>
@@ -6792,72 +6792,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4975</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2404</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5688</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>87,46%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>42,26%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>696</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>4975</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2766</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>5688</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>87,46%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3433</t>
+          <t>3468</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -6905,57 +6905,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5688</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5688</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>5688</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>696</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>696</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>696</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>5688</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>5688</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>5688</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7022,72 +7022,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3137</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,77%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>25,44%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1389</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3763</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3464</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>17,28%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>46,82%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3022</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,77%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>584</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5505</t>
+          <t>5265</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>25,84%</t>
         </is>
       </c>
     </row>
@@ -7135,74 +7135,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11744</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9195</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>12332</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,23%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>74,56%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>6649</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>4275</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>4574</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>8038</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>82,72%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>53,18%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>56,9%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>11744</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>9310</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>12332</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,23%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>75,49%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>28</t>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14866</t>
+          <t>15106</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19795</t>
+          <t>19787</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -7248,57 +7248,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>12332</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>12332</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>12332</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>8038</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>8038</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>8038</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>12332</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>12332</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>12332</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7365,107 +7365,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1362</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3665</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3869</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>20,66%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>55,61%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>58,71%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1362</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>4207</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>8,83%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1362</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4561</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>8,83%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>27,28%</t>
         </is>
       </c>
     </row>
@@ -7478,74 +7478,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>8835</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>5228</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>2925</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2721</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>6590</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>79,34%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>44,39%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>41,29%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>8835</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>20</t>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10864</t>
+          <t>11218</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7591,57 +7591,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>8835</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>8835</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>8835</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>6590</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>6590</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>6590</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>8835</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>8835</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>8835</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7821,47 +7821,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>5220</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>573</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>5220</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -7934,57 +7934,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>5220</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>5220</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>5220</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>573</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>573</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>573</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>5220</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>5220</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>5220</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8051,72 +8051,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>4004</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>9,83%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>2751</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>645</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5880</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5791</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>12,43%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>26,58%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>4041</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8175</t>
+          <t>8277</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -8164,72 +8164,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>39423</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>36720</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>40724</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>96,81%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>90,17%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>19372</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>16243</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>21478</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>16332</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>21422</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>87,57%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>73,42%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>97,09%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>39423</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>36683</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>40724</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>96,81%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>54672</t>
+          <t>54570</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>61439</t>
+          <t>61451</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -8277,57 +8277,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>40724</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>40724</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>40724</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>22123</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>22123</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>22123</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>40724</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>40724</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>40724</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8449,7 +8449,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -8460,7 +8460,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>568</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>2369</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>689</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1452</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3964</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,5%</t>
         </is>
       </c>
     </row>
@@ -8746,27 +8746,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>2787</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>987</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3512</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -8781,27 +8781,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>790</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>3482</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -8816,27 +8816,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>5696</t>
+          <t>5580</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>3043</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7148</t>
+          <t>6837</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3512</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3512</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3512</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>3482</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>3482</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>3482</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>7148</t>
+          <t>6837</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7148</t>
+          <t>6837</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7148</t>
+          <t>6837</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8971,107 +8971,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>988</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3879</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>14,71%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1012</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4432</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>14,03%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>988</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3936</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>10,64%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>61,44%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1012</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4111</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>10,39%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,39%</t>
         </is>
       </c>
     </row>
@@ -9084,72 +9084,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5730</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2831</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6718</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>85,29%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>42,15%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2533</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>6201</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2794</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>7213</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>85,97%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,27 +9159,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>8734</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5635</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9746</t>
+          <t>9287</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -9197,57 +9197,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>6718</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>6718</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>6718</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2533</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>2533</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2533</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7213</t>
+          <t>2569</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7213</t>
+          <t>2569</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7213</t>
+          <t>2569</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>9746</t>
+          <t>9287</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>9746</t>
+          <t>9287</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9746</t>
+          <t>9287</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9427,64 +9427,64 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3550</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>735</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>766</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>3657</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -9502,7 +9502,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4392</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -9540,57 +9540,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3550</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3550</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3550</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>735</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>735</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>735</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3657</t>
+          <t>766</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3657</t>
+          <t>766</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3657</t>
+          <t>766</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>4392</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4392</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4392</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9657,107 +9657,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3048</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>11,08%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2876</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>11,38%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>57,29%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>55,27%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3067</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>5,11%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3425</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>4,73%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>26,46%</t>
         </is>
       </c>
     </row>
@@ -9770,74 +9770,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6389</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>4730</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2260</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5320</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>88,92%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>42,49%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>4612</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2331</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5204</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>88,62%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>44,79%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>7151</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>15</t>
@@ -9845,27 +9845,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>11881</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9046</t>
+          <t>8526</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12471</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>6389</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>6389</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>6389</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7151</t>
+          <t>5204</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7151</t>
+          <t>5204</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7151</t>
+          <t>5204</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>12471</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>12471</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>12471</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10113,64 +10113,64 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1783</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>2677</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2587</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -10188,7 +10188,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4503</t>
+          <t>4369</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -10226,57 +10226,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1783</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1783</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1783</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2677</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>2677</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>2677</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>2587</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>2587</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>2587</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>4503</t>
+          <t>4369</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4503</t>
+          <t>4369</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4503</t>
+          <t>4369</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10456,64 +10456,64 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>2375</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>2577</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -10531,7 +10531,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>3032</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -10569,57 +10569,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>2375</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>2375</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>2375</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>3032</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>3032</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>3032</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>1557</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4444</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,7 +10726,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -10736,12 +10736,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5821</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -10751,7 +10751,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>990</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7244</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>16,81%</t>
         </is>
       </c>
     </row>
@@ -10799,74 +10799,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>20694</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>16888</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>93,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>75,9%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>15807</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>12707</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>17151</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>92,17%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>74,09%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>15903</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>13129</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>17184</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>92,55%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>76,4%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>22324</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>18213</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>24034</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>92,88%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>75,78%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>51</t>
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>38131</t>
+          <t>36597</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>33941</t>
+          <t>32807</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>40161</t>
+          <t>38445</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,49%</t>
         </is>
       </c>
     </row>
@@ -10912,57 +10912,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>17151</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>17151</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>17151</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>24034</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>24034</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24034</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>41185</t>
+          <t>39435</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>41185</t>
+          <t>39435</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>41185</t>
+          <t>39435</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
